--- a/src/test/resources/Testdata.xlsx
+++ b/src/test/resources/Testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shazk\IdeaProjects\javaSeleniumPOM\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89918E96-9843-4468-A09D-0ED83463AC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B99D7F-BB91-48D6-9946-327717E69C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3A835458-F41A-47CE-B000-DDA73FF159BB}"/>
   </bookViews>
@@ -25,21 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>standard_user</t>
   </si>
   <si>
     <t>secret_sauce</t>
-  </si>
-  <si>
-    <t>locked_out_user</t>
-  </si>
-  <si>
-    <t>invalid_user</t>
-  </si>
-  <si>
-    <t>wrong_pass</t>
   </si>
 </sst>
 </file>
@@ -392,7 +383,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8DEB3B-B89E-4E7E-9D94-76BB37C37770}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.21875" customWidth="1"/>
@@ -410,22 +401,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
